--- a/astro-site/public/dl/kit-tareas-bar/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/02-partidas-cocina.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Coctelería Clásica" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cerveza y Grifo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Vinos y Bodega" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coctelería Clásica" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cerveza y Grifo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vinos y Bodega" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Coctelería Clásica'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cerveza y Grifo'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Vinos y Bodega'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -131,7 +135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -153,59 +157,118 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="28">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -565,15 +628,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -581,6 +645,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -609,8 +674,33 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -619,18 +709,18 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -647,10 +737,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -675,7 +766,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -690,18 +781,16 @@
           <t xml:space="preserve">  Pre-Servicio Coctelería</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -727,10 +816,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -756,10 +843,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -785,10 +870,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -814,10 +897,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -843,10 +924,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -872,10 +951,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -900,24 +977,23 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="15" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Durante el Servicio</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="B14" s="25" t="n"/>
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="26" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -943,10 +1019,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -972,10 +1046,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1001,10 +1073,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="27" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1030,10 +1100,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="27" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1058,6 +1126,8 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="15" t="n"/>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
@@ -1066,17 +1136,19 @@
       </c>
       <c r="D22" s="16">
         <f>COUNTIF(F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22" s="16" t="n">
-        <v>12</v>
-      </c>
-    </row>
+      <c r="F22" s="16">
+        <f>COUNTIF(B5:B20,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
@@ -1084,13 +1156,17 @@
         </is>
       </c>
       <c r="B24" s="15" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="26" t="n"/>
       <c r="E24" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-    </row>
+      <c r="G24" s="26" t="n"/>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
@@ -1108,12 +1184,26 @@
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1122,18 +1212,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1150,10 +1240,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1178,7 +1269,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1193,18 +1284,16 @@
           <t xml:space="preserve">  Preparación</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1230,10 +1319,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1259,10 +1346,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1288,10 +1373,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1317,10 +1400,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1346,10 +1427,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1374,24 +1453,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Control de Stock de Botella</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="23" t="n"/>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1417,10 +1495,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1446,10 +1522,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1475,10 +1549,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1503,6 +1575,8 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
@@ -1511,17 +1585,19 @@
       </c>
       <c r="D20" s="16">
         <f>COUNTIF(F5:F18,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F20" s="16" t="n">
-        <v>10</v>
-      </c>
-    </row>
+      <c r="F20" s="16">
+        <f>COUNTIF(B5:B18,"?*")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
@@ -1529,13 +1605,17 @@
         </is>
       </c>
       <c r="B22" s="15" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="26" t="n"/>
       <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F22" s="15" t="n"/>
-    </row>
+      <c r="G22" s="26" t="n"/>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
@@ -1553,12 +1633,26 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="F22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1567,18 +1661,18 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1595,10 +1689,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1623,7 +1718,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1638,18 +1733,16 @@
           <t xml:space="preserve">  Vinos por Copa</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="n"/>
-      <c r="G5" s="23" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1675,10 +1768,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1704,10 +1795,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1733,10 +1822,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1762,10 +1849,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1790,24 +1875,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Bodega y Reservas</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1833,10 +1917,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1862,10 +1944,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1891,10 +1971,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1919,6 +1997,8 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
@@ -1927,17 +2007,19 @@
       </c>
       <c r="D19" s="16">
         <f>COUNTIF(F5:F17,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F19" s="16" t="n">
-        <v>9</v>
-      </c>
-    </row>
+      <c r="F19" s="16">
+        <f>COUNTIF(B5:B17,"?*")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
@@ -1945,13 +2027,17 @@
         </is>
       </c>
       <c r="B21" s="15" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="26" t="n"/>
       <c r="E21" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F21" s="15" t="n"/>
-    </row>
+      <c r="G21" s="26" t="n"/>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
@@ -1969,11 +2055,25 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G17">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-bar/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/02-partidas-cocina.xlsx
@@ -13,9 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vinos y Bodega" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Coctelería Clásica'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Coctelería Clásica'!$A$1:$G$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cerveza y Grifo'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cerveza y Grifo'!$A$1:$G$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Vinos y Bodega'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Vinos y Bodega'!$A$1:$G$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,8 +100,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -132,6 +150,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F3E5F5"/>
         <bgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -205,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -253,6 +276,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,63 +714,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>02 — Partidas de Barra · Bar / Cocktails</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Tareas organizadas por área de servicio.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>▸ Cada pestaña cubre una zona específica del bar</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>▸ Las tareas están ordenadas cronológicamente</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>▸ Personaliza con la carta de cócteles de tu bar</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="B9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>▸ Estás en 02-partidas-cocina.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -711,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -761,7 +978,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -776,421 +993,501 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pre-Servicio Coctelería</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Verificar stock de spirits base: ginebra, vodka, ron, tequila, whisky, brandy</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Verificar stock de vermut (rojo, blanco, dry), amargos y licores</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Preparar batch de cócteles de alta rotación (Negroni, Margarita pre-mix)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Preparar infusiones del día (si aplica: gin infusionado, vodka con especias)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Preparar jarabes especiales: miel-jengibre, canela, lavanda, orgeat</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Verificar stock de bitter: Angostura, Peychaud, Orange bitters</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Tener por escrito los alérgenos de la carta de cócteles y que todo el equipo sepa dónde consultarlos: el orgeat lleva ALMENDRA, los sours CLARA DE HUEVO, los flips LÁCTEOS y los vinos y vermuts SULFITOS</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>Head Bartender</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="39" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Verificar stock de bitters: Angostura, Peychaud's y orange bitters</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>Coctelería</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="39" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Preparar twist de cítricos frescos (piel de limón, naranja, pomelo)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="40" t="n"/>
+      <c r="B14" s="40" t="n"/>
+      <c r="C14" s="40" t="n"/>
+      <c r="D14" s="40" t="n"/>
+      <c r="E14" s="40" t="n"/>
+      <c r="F14" s="40" t="n"/>
+      <c r="G14" s="40" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Durante el Servicio</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="26" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="32" t="n"/>
+      <c r="C15" s="32" t="n"/>
+      <c r="D15" s="32" t="n"/>
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="33" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Mantener speed rail organizado y botellas orientadas (etiqueta al frente)</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Reponer hielo cada hora (o antes si hay pico)</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Reponer hielo cada hora (o antes si hay pico) SIEMPRE con pala o pinzas, nunca con el vaso: un vaso roto obliga a vaciar la cubeta entera</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Reponer garnish y mise en place</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Controlar calidad de cada cóctel antes de servir (prueba visual y aroma)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Mantener estación limpia entre cócteles (wipe, organizar)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>Coctelería</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D20" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="n"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="41" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="n"/>
+      <c r="B23" s="42" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="41" t="n"/>
+      <c r="B24" s="42" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="n"/>
+      <c r="B25" s="42" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="38" t="n"/>
+      <c r="G25" s="39" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D22" s="16">
-        <f>COUNTIF(F5:F20,"✓")</f>
+      <c r="D27" s="16">
+        <f>COUNTIFS(B5:B25,"?*",F5:F25,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22" s="16">
-        <f>COUNTIF(B5:B20,"?*")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="F27" s="16">
+        <f>COUNTIF(B5:B25,"?*")-COUNTIF(F5:F25,"N/A")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="B29" s="43" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="26" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="F29" s="43" t="n"/>
+      <c r="G29" s="26" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B24:D24"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A27:C27"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G20">
+  <conditionalFormatting sqref="A5:G25">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1214,7 +1511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1279,367 +1576,420 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">  Preparación</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Verificar presión de CO₂ de barriles (2.5-3.0 bar)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Verificar presión de CO₂ de barriles (2,5-3,0 bar)</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Purgar grifos: tirar primer tercio hasta que salga limpio</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Verificar temperatura de barriles en cámara (3-5 °C)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Verificar temperatura de barriles en cámara (3-5 °C) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Verificar stock de barriles de reserva por marca</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Limpiar boquillas de grifo con agua caliente</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Preparar cristalería de cerveza (congelar copas si es estilo del bar)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
-    </row>
-    <row r="12"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="39" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="n"/>
+      <c r="B12" s="40" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
+      <c r="G12" s="40" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  Control de Stock de Botella</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="26" t="n"/>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Verificar stock de cerveza en botella y lata en cámara</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Reponer cámara de barra con stock de bodega</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Verificar stock de refrescos: tónica, soda, cola, ginger ale, ginger beer</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Verificar stock de agua mineral y con gas</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="n"/>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D20" s="16">
-        <f>COUNTIF(F5:F18,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F20" s="16">
-        <f>COUNTIF(B5:B18,"?*")</f>
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="A20" s="41" t="n"/>
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="n"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="26" t="n"/>
+      <c r="A22" s="41" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
     </row>
     <row r="23"/>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D24" s="16">
+        <f>COUNTIFS(B5:B22,"?*",F5:F22,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F24" s="16">
+        <f>COUNTIF(B5:B22,"?*")-COUNTIF(F5:F22,"N/A")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="26" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G18">
+  <conditionalFormatting sqref="A5:G22">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1663,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1685,7 +2035,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1713,7 +2063,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1728,340 +2078,393 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  Vinos por Copa</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Verificar vinos abiertos por copa (blancos y rosados en cámara a 8-10 °C)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Verificar vinos tintos abiertos (temperatura ambiente o 16-18 °C)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Comprobar que ningún vino abierto tiene más de 3 días (oler, probar)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Abrir botellas nuevas si quedan menos de 2 copas de algún vino</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Actualizar pizarra de vinos por copa (si cambió alguno)</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>16:30</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  Bodega y Reservas</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Verificar temperatura de bodega / vinoteca (12-16 °C)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Revisar stock de vinos de carta (marcar los agotados)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Bartender</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>Semanal</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Organizar botellas por zona/denominación</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Barback</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>Semanal</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Revisar estado de vinos especiales / añadas</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Bodega</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Head Bartender</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="n"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D19" s="16">
-        <f>COUNTIF(F5:F17,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F19" s="16">
-        <f>COUNTIF(B5:B17,"?*")</f>
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="20"/>
+      <c r="A19" s="41" t="n"/>
+      <c r="B19" s="42" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="n"/>
+      <c r="B20" s="42" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
+    </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="26" t="n"/>
+      <c r="A21" s="41" t="n"/>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="36" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D23" s="16">
+        <f>COUNTIFS(B5:B21,"?*",F5:F21,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F23" s="16">
+        <f>COUNTIF(B5:B21,"?*")-COUNTIF(F5:F21,"N/A")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="26" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
-    <mergeCell ref="F21:G21"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="F25:G25"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="B25:D25"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G17">
+  <conditionalFormatting sqref="A5:G21">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F19 F20 F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
